--- a/artfynd/A 8305-2022 artfynd.xlsx
+++ b/artfynd/A 8305-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119945182</v>
+        <v>119945424</v>
       </c>
       <c r="B2" t="n">
-        <v>78526</v>
+        <v>91856</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>2059</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>435945</v>
+        <v>435856</v>
       </c>
       <c r="R2" t="n">
-        <v>6708988</v>
+        <v>6709035</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119945518</v>
+        <v>119945174</v>
       </c>
       <c r="B3" t="n">
-        <v>86412</v>
+        <v>78526</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3690</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>435894</v>
+        <v>435945</v>
       </c>
       <c r="R3" t="n">
-        <v>6709005</v>
+        <v>6708988</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119945909</v>
+        <v>119945284</v>
       </c>
       <c r="B4" t="n">
-        <v>91884</v>
+        <v>78526</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5449</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>435898</v>
+        <v>435879</v>
       </c>
       <c r="R4" t="n">
-        <v>6709012</v>
+        <v>6709025</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119945222</v>
+        <v>119945297</v>
       </c>
       <c r="B5" t="n">
-        <v>8432</v>
+        <v>78526</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>435948</v>
+        <v>435871</v>
       </c>
       <c r="R5" t="n">
-        <v>6708984</v>
+        <v>6709030</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119945192</v>
+        <v>119945222</v>
       </c>
       <c r="B6" t="n">
-        <v>78263</v>
+        <v>8432</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>435942</v>
+        <v>435948</v>
       </c>
       <c r="R6" t="n">
-        <v>6708975</v>
+        <v>6708984</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119945189</v>
+        <v>119945192</v>
       </c>
       <c r="B7" t="n">
-        <v>79144</v>
+        <v>78263</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>435946</v>
+        <v>435942</v>
       </c>
       <c r="R7" t="n">
-        <v>6708981</v>
+        <v>6708975</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119945284</v>
+        <v>119945189</v>
       </c>
       <c r="B8" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>435879</v>
+        <v>435946</v>
       </c>
       <c r="R8" t="n">
-        <v>6709025</v>
+        <v>6708981</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119945297</v>
+        <v>119945909</v>
       </c>
       <c r="B9" t="n">
-        <v>78526</v>
+        <v>91884</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>5449</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>435871</v>
+        <v>435898</v>
       </c>
       <c r="R9" t="n">
-        <v>6709030</v>
+        <v>6709012</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119945424</v>
+        <v>119945518</v>
       </c>
       <c r="B10" t="n">
-        <v>91856</v>
+        <v>86412</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2059</v>
+        <v>3690</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>435856</v>
+        <v>435894</v>
       </c>
       <c r="R10" t="n">
-        <v>6709035</v>
+        <v>6709005</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 8305-2022 artfynd.xlsx
+++ b/artfynd/A 8305-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119945424</v>
+        <v>119945297</v>
       </c>
       <c r="B2" t="n">
-        <v>91856</v>
+        <v>78526</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2059</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>435856</v>
+        <v>435871</v>
       </c>
       <c r="R2" t="n">
-        <v>6709035</v>
+        <v>6709030</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119945174</v>
+        <v>119945284</v>
       </c>
       <c r="B3" t="n">
         <v>78526</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>435945</v>
+        <v>435879</v>
       </c>
       <c r="R3" t="n">
-        <v>6708988</v>
+        <v>6709025</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119945284</v>
+        <v>119945182</v>
       </c>
       <c r="B4" t="n">
         <v>78526</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>435879</v>
+        <v>435945</v>
       </c>
       <c r="R4" t="n">
-        <v>6709025</v>
+        <v>6708988</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119945297</v>
+        <v>119945909</v>
       </c>
       <c r="B5" t="n">
-        <v>78526</v>
+        <v>91884</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5449</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>435871</v>
+        <v>435898</v>
       </c>
       <c r="R5" t="n">
-        <v>6709030</v>
+        <v>6709012</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119945222</v>
+        <v>119945518</v>
       </c>
       <c r="B6" t="n">
-        <v>8432</v>
+        <v>86412</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>3690</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>435948</v>
+        <v>435894</v>
       </c>
       <c r="R6" t="n">
-        <v>6708984</v>
+        <v>6709005</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119945192</v>
+        <v>119945189</v>
       </c>
       <c r="B7" t="n">
-        <v>78263</v>
+        <v>79144</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>435942</v>
+        <v>435946</v>
       </c>
       <c r="R7" t="n">
-        <v>6708975</v>
+        <v>6708981</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119945189</v>
+        <v>119945424</v>
       </c>
       <c r="B8" t="n">
-        <v>79144</v>
+        <v>91856</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>2059</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>435946</v>
+        <v>435856</v>
       </c>
       <c r="R8" t="n">
-        <v>6708981</v>
+        <v>6709035</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119945909</v>
+        <v>119945222</v>
       </c>
       <c r="B9" t="n">
-        <v>91884</v>
+        <v>8432</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5449</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>435898</v>
+        <v>435948</v>
       </c>
       <c r="R9" t="n">
-        <v>6709012</v>
+        <v>6708984</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119945518</v>
+        <v>119945192</v>
       </c>
       <c r="B10" t="n">
-        <v>86412</v>
+        <v>78263</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3690</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>435894</v>
+        <v>435942</v>
       </c>
       <c r="R10" t="n">
-        <v>6709005</v>
+        <v>6708975</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 8305-2022 artfynd.xlsx
+++ b/artfynd/A 8305-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119945297</v>
+        <v>119945424</v>
       </c>
       <c r="B2" t="n">
-        <v>78526</v>
+        <v>91856</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>2059</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>435871</v>
+        <v>435856</v>
       </c>
       <c r="R2" t="n">
-        <v>6709030</v>
+        <v>6709035</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119945284</v>
+        <v>119945189</v>
       </c>
       <c r="B3" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>435879</v>
+        <v>435946</v>
       </c>
       <c r="R3" t="n">
-        <v>6709025</v>
+        <v>6708981</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119945518</v>
+        <v>119945297</v>
       </c>
       <c r="B6" t="n">
-        <v>86412</v>
+        <v>78526</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3690</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>435894</v>
+        <v>435871</v>
       </c>
       <c r="R6" t="n">
-        <v>6709005</v>
+        <v>6709030</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119945189</v>
+        <v>119945222</v>
       </c>
       <c r="B7" t="n">
-        <v>79144</v>
+        <v>8432</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>435946</v>
+        <v>435948</v>
       </c>
       <c r="R7" t="n">
-        <v>6708981</v>
+        <v>6708984</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119945424</v>
+        <v>119945518</v>
       </c>
       <c r="B8" t="n">
-        <v>91856</v>
+        <v>86412</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2059</v>
+        <v>3690</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>435856</v>
+        <v>435894</v>
       </c>
       <c r="R8" t="n">
-        <v>6709035</v>
+        <v>6709005</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119945222</v>
+        <v>119945284</v>
       </c>
       <c r="B9" t="n">
-        <v>8432</v>
+        <v>78526</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>435948</v>
+        <v>435879</v>
       </c>
       <c r="R9" t="n">
-        <v>6708984</v>
+        <v>6709025</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 8305-2022 artfynd.xlsx
+++ b/artfynd/A 8305-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119945424</v>
+        <v>119945189</v>
       </c>
       <c r="B2" t="n">
-        <v>91856</v>
+        <v>79144</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2059</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>435856</v>
+        <v>435946</v>
       </c>
       <c r="R2" t="n">
-        <v>6709035</v>
+        <v>6708981</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119945189</v>
+        <v>119945424</v>
       </c>
       <c r="B3" t="n">
-        <v>79144</v>
+        <v>91856</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>2059</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>435946</v>
+        <v>435856</v>
       </c>
       <c r="R3" t="n">
-        <v>6708981</v>
+        <v>6709035</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 8305-2022 artfynd.xlsx
+++ b/artfynd/A 8305-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119945189</v>
+        <v>119945424</v>
       </c>
       <c r="B2" t="n">
-        <v>79144</v>
+        <v>91856</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>2059</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>435946</v>
+        <v>435856</v>
       </c>
       <c r="R2" t="n">
-        <v>6708981</v>
+        <v>6709035</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119945424</v>
+        <v>119945189</v>
       </c>
       <c r="B3" t="n">
-        <v>91856</v>
+        <v>79144</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2059</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>435856</v>
+        <v>435946</v>
       </c>
       <c r="R3" t="n">
-        <v>6709035</v>
+        <v>6708981</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 8305-2022 artfynd.xlsx
+++ b/artfynd/A 8305-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119945189</v>
+        <v>119945284</v>
       </c>
       <c r="B2" t="n">
-        <v>79144</v>
+        <v>78542</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>435946</v>
+        <v>435879</v>
       </c>
       <c r="R2" t="n">
-        <v>6708981</v>
+        <v>6709025</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119945424</v>
+        <v>119945518</v>
       </c>
       <c r="B3" t="n">
-        <v>91856</v>
+        <v>86429</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2059</v>
+        <v>3690</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>435856</v>
+        <v>435894</v>
       </c>
       <c r="R3" t="n">
-        <v>6709035</v>
+        <v>6709005</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119945182</v>
+        <v>119945297</v>
       </c>
       <c r="B4" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>435945</v>
+        <v>435871</v>
       </c>
       <c r="R4" t="n">
-        <v>6708988</v>
+        <v>6709030</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119945909</v>
+        <v>119945189</v>
       </c>
       <c r="B5" t="n">
-        <v>91884</v>
+        <v>79160</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5449</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>435898</v>
+        <v>435946</v>
       </c>
       <c r="R5" t="n">
-        <v>6709012</v>
+        <v>6708981</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119945297</v>
+        <v>119945424</v>
       </c>
       <c r="B6" t="n">
-        <v>78526</v>
+        <v>91874</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>2059</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>435871</v>
+        <v>435856</v>
       </c>
       <c r="R6" t="n">
-        <v>6709030</v>
+        <v>6709035</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119945518</v>
+        <v>119945182</v>
       </c>
       <c r="B8" t="n">
-        <v>86412</v>
+        <v>78542</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3690</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>435894</v>
+        <v>435945</v>
       </c>
       <c r="R8" t="n">
-        <v>6709005</v>
+        <v>6708988</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119945284</v>
+        <v>119945192</v>
       </c>
       <c r="B9" t="n">
-        <v>78526</v>
+        <v>78279</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>435879</v>
+        <v>435942</v>
       </c>
       <c r="R9" t="n">
-        <v>6709025</v>
+        <v>6708975</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119945192</v>
+        <v>119945909</v>
       </c>
       <c r="B10" t="n">
-        <v>78263</v>
+        <v>91902</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>5449</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>435942</v>
+        <v>435898</v>
       </c>
       <c r="R10" t="n">
-        <v>6708975</v>
+        <v>6709012</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 8305-2022 artfynd.xlsx
+++ b/artfynd/A 8305-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119945284</v>
+        <v>119945424</v>
       </c>
       <c r="B2" t="n">
-        <v>78542</v>
+        <v>91874</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>2059</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>435879</v>
+        <v>435856</v>
       </c>
       <c r="R2" t="n">
-        <v>6709025</v>
+        <v>6709035</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119945518</v>
+        <v>119945297</v>
       </c>
       <c r="B3" t="n">
-        <v>86429</v>
+        <v>78542</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3690</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>435894</v>
+        <v>435871</v>
       </c>
       <c r="R3" t="n">
-        <v>6709005</v>
+        <v>6709030</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119945297</v>
+        <v>119945909</v>
       </c>
       <c r="B4" t="n">
-        <v>78542</v>
+        <v>91902</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5449</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>435871</v>
+        <v>435898</v>
       </c>
       <c r="R4" t="n">
-        <v>6709030</v>
+        <v>6709012</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119945189</v>
+        <v>119945174</v>
       </c>
       <c r="B5" t="n">
-        <v>79160</v>
+        <v>78542</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>435946</v>
+        <v>435945</v>
       </c>
       <c r="R5" t="n">
-        <v>6708981</v>
+        <v>6708988</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119945424</v>
+        <v>119945518</v>
       </c>
       <c r="B6" t="n">
-        <v>91874</v>
+        <v>86429</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2059</v>
+        <v>3690</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>435856</v>
+        <v>435894</v>
       </c>
       <c r="R6" t="n">
-        <v>6709035</v>
+        <v>6709005</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119945222</v>
+        <v>119945284</v>
       </c>
       <c r="B7" t="n">
-        <v>8432</v>
+        <v>78542</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>435948</v>
+        <v>435879</v>
       </c>
       <c r="R7" t="n">
-        <v>6708984</v>
+        <v>6709025</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119945182</v>
+        <v>119945189</v>
       </c>
       <c r="B8" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>435945</v>
+        <v>435946</v>
       </c>
       <c r="R8" t="n">
-        <v>6708988</v>
+        <v>6708981</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119945909</v>
+        <v>119945222</v>
       </c>
       <c r="B10" t="n">
-        <v>91902</v>
+        <v>8432</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,25 +1503,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5449</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>435898</v>
+        <v>435948</v>
       </c>
       <c r="R10" t="n">
-        <v>6709012</v>
+        <v>6708984</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 8305-2022 artfynd.xlsx
+++ b/artfynd/A 8305-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119945424</v>
+        <v>119945222</v>
       </c>
       <c r="B2" t="n">
-        <v>91874</v>
+        <v>8432</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2059</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>435856</v>
+        <v>435948</v>
       </c>
       <c r="R2" t="n">
-        <v>6709035</v>
+        <v>6708984</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119945297</v>
+        <v>119945424</v>
       </c>
       <c r="B3" t="n">
-        <v>78542</v>
+        <v>91874</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>2059</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>435871</v>
+        <v>435856</v>
       </c>
       <c r="R3" t="n">
-        <v>6709030</v>
+        <v>6709035</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119945909</v>
+        <v>119945174</v>
       </c>
       <c r="B4" t="n">
-        <v>91902</v>
+        <v>78542</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5449</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>435898</v>
+        <v>435945</v>
       </c>
       <c r="R4" t="n">
-        <v>6709012</v>
+        <v>6708988</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119945174</v>
+        <v>119945909</v>
       </c>
       <c r="B5" t="n">
-        <v>78542</v>
+        <v>91902</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5449</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>435945</v>
+        <v>435898</v>
       </c>
       <c r="R5" t="n">
-        <v>6708988</v>
+        <v>6709012</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119945518</v>
+        <v>119945189</v>
       </c>
       <c r="B6" t="n">
-        <v>86429</v>
+        <v>79160</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3690</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>435894</v>
+        <v>435946</v>
       </c>
       <c r="R6" t="n">
-        <v>6709005</v>
+        <v>6708981</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119945284</v>
+        <v>119945518</v>
       </c>
       <c r="B7" t="n">
-        <v>78542</v>
+        <v>86429</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>3690</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>435879</v>
+        <v>435894</v>
       </c>
       <c r="R7" t="n">
-        <v>6709025</v>
+        <v>6709005</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119945189</v>
+        <v>119945284</v>
       </c>
       <c r="B8" t="n">
-        <v>79160</v>
+        <v>78542</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>435946</v>
+        <v>435879</v>
       </c>
       <c r="R8" t="n">
-        <v>6708981</v>
+        <v>6709025</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119945222</v>
+        <v>119945297</v>
       </c>
       <c r="B10" t="n">
-        <v>8432</v>
+        <v>78542</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,25 +1503,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>435948</v>
+        <v>435871</v>
       </c>
       <c r="R10" t="n">
-        <v>6708984</v>
+        <v>6709030</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 8305-2022 artfynd.xlsx
+++ b/artfynd/A 8305-2022 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119945424</v>
+        <v>119945182</v>
       </c>
       <c r="B3" t="n">
-        <v>91874</v>
+        <v>78542</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2059</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>435856</v>
+        <v>435945</v>
       </c>
       <c r="R3" t="n">
-        <v>6709035</v>
+        <v>6708988</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119945174</v>
+        <v>119945909</v>
       </c>
       <c r="B4" t="n">
-        <v>78542</v>
+        <v>91902</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5449</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>435945</v>
+        <v>435898</v>
       </c>
       <c r="R4" t="n">
-        <v>6708988</v>
+        <v>6709012</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119945909</v>
+        <v>119945284</v>
       </c>
       <c r="B5" t="n">
-        <v>91902</v>
+        <v>78542</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5449</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>435898</v>
+        <v>435879</v>
       </c>
       <c r="R5" t="n">
-        <v>6709012</v>
+        <v>6709025</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119945189</v>
+        <v>119945518</v>
       </c>
       <c r="B6" t="n">
-        <v>79160</v>
+        <v>86429</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>3690</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>435946</v>
+        <v>435894</v>
       </c>
       <c r="R6" t="n">
-        <v>6708981</v>
+        <v>6709005</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119945518</v>
+        <v>119945424</v>
       </c>
       <c r="B7" t="n">
-        <v>86429</v>
+        <v>91874</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3690</v>
+        <v>2059</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>435894</v>
+        <v>435856</v>
       </c>
       <c r="R7" t="n">
-        <v>6709005</v>
+        <v>6709035</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119945284</v>
+        <v>119945189</v>
       </c>
       <c r="B8" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>435879</v>
+        <v>435946</v>
       </c>
       <c r="R8" t="n">
-        <v>6709025</v>
+        <v>6708981</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 8305-2022 artfynd.xlsx
+++ b/artfynd/A 8305-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119945222</v>
+        <v>119945297</v>
       </c>
       <c r="B2" t="n">
-        <v>8432</v>
+        <v>78542</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>435948</v>
+        <v>435871</v>
       </c>
       <c r="R2" t="n">
-        <v>6708984</v>
+        <v>6709030</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119945182</v>
+        <v>119945518</v>
       </c>
       <c r="B3" t="n">
-        <v>78542</v>
+        <v>86429</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>3690</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>435945</v>
+        <v>435894</v>
       </c>
       <c r="R3" t="n">
-        <v>6708988</v>
+        <v>6709005</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119945909</v>
+        <v>119945424</v>
       </c>
       <c r="B4" t="n">
-        <v>91902</v>
+        <v>91874</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5449</v>
+        <v>2059</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>435898</v>
+        <v>435856</v>
       </c>
       <c r="R4" t="n">
-        <v>6709012</v>
+        <v>6709035</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119945284</v>
+        <v>119945189</v>
       </c>
       <c r="B5" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>435879</v>
+        <v>435946</v>
       </c>
       <c r="R5" t="n">
-        <v>6709025</v>
+        <v>6708981</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119945518</v>
+        <v>119945192</v>
       </c>
       <c r="B6" t="n">
-        <v>86429</v>
+        <v>78279</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3690</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>435894</v>
+        <v>435942</v>
       </c>
       <c r="R6" t="n">
-        <v>6709005</v>
+        <v>6708975</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119945424</v>
+        <v>119945284</v>
       </c>
       <c r="B7" t="n">
-        <v>91874</v>
+        <v>78542</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2059</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>435856</v>
+        <v>435879</v>
       </c>
       <c r="R7" t="n">
-        <v>6709035</v>
+        <v>6709025</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119945189</v>
+        <v>119945174</v>
       </c>
       <c r="B8" t="n">
-        <v>79160</v>
+        <v>78542</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>435946</v>
+        <v>435945</v>
       </c>
       <c r="R8" t="n">
-        <v>6708981</v>
+        <v>6708988</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119945192</v>
+        <v>119945222</v>
       </c>
       <c r="B9" t="n">
-        <v>78279</v>
+        <v>8432</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>435942</v>
+        <v>435948</v>
       </c>
       <c r="R9" t="n">
-        <v>6708975</v>
+        <v>6708984</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119945297</v>
+        <v>119945909</v>
       </c>
       <c r="B10" t="n">
-        <v>78542</v>
+        <v>91902</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>5449</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>435871</v>
+        <v>435898</v>
       </c>
       <c r="R10" t="n">
-        <v>6709030</v>
+        <v>6709012</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 8305-2022 artfynd.xlsx
+++ b/artfynd/A 8305-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119945297</v>
+        <v>119945189</v>
       </c>
       <c r="B2" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>435871</v>
+        <v>435946</v>
       </c>
       <c r="R2" t="n">
-        <v>6709030</v>
+        <v>6708981</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119945518</v>
+        <v>119945284</v>
       </c>
       <c r="B3" t="n">
-        <v>86429</v>
+        <v>78542</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3690</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>435894</v>
+        <v>435879</v>
       </c>
       <c r="R3" t="n">
-        <v>6709005</v>
+        <v>6709025</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119945424</v>
+        <v>119945182</v>
       </c>
       <c r="B4" t="n">
-        <v>91874</v>
+        <v>78542</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2059</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>435856</v>
+        <v>435945</v>
       </c>
       <c r="R4" t="n">
-        <v>6709035</v>
+        <v>6708988</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119945189</v>
+        <v>119945909</v>
       </c>
       <c r="B5" t="n">
-        <v>79160</v>
+        <v>91902</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>5449</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>435946</v>
+        <v>435898</v>
       </c>
       <c r="R5" t="n">
-        <v>6708981</v>
+        <v>6709012</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119945192</v>
+        <v>119945297</v>
       </c>
       <c r="B6" t="n">
-        <v>78279</v>
+        <v>78542</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>435942</v>
+        <v>435871</v>
       </c>
       <c r="R6" t="n">
-        <v>6708975</v>
+        <v>6709030</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119945284</v>
+        <v>119945222</v>
       </c>
       <c r="B7" t="n">
-        <v>78542</v>
+        <v>8432</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>435879</v>
+        <v>435948</v>
       </c>
       <c r="R7" t="n">
-        <v>6709025</v>
+        <v>6708984</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119945174</v>
+        <v>119945518</v>
       </c>
       <c r="B8" t="n">
-        <v>78542</v>
+        <v>86429</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>3690</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>435945</v>
+        <v>435894</v>
       </c>
       <c r="R8" t="n">
-        <v>6708988</v>
+        <v>6709005</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119945222</v>
+        <v>119945424</v>
       </c>
       <c r="B9" t="n">
-        <v>8432</v>
+        <v>91874</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>2059</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>435948</v>
+        <v>435856</v>
       </c>
       <c r="R9" t="n">
-        <v>6708984</v>
+        <v>6709035</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119945909</v>
+        <v>119945192</v>
       </c>
       <c r="B10" t="n">
-        <v>91902</v>
+        <v>78279</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5449</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>435898</v>
+        <v>435942</v>
       </c>
       <c r="R10" t="n">
-        <v>6709012</v>
+        <v>6708975</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 8305-2022 artfynd.xlsx
+++ b/artfynd/A 8305-2022 artfynd.xlsx
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119945284</v>
+        <v>119945182</v>
       </c>
       <c r="B3" t="n">
         <v>78542</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>435879</v>
+        <v>435945</v>
       </c>
       <c r="R3" t="n">
-        <v>6709025</v>
+        <v>6708988</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119945182</v>
+        <v>119945518</v>
       </c>
       <c r="B4" t="n">
-        <v>78542</v>
+        <v>86429</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>3690</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>435945</v>
+        <v>435894</v>
       </c>
       <c r="R4" t="n">
-        <v>6708988</v>
+        <v>6709005</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119945909</v>
+        <v>119945424</v>
       </c>
       <c r="B5" t="n">
-        <v>91902</v>
+        <v>91874</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5449</v>
+        <v>2059</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>435898</v>
+        <v>435856</v>
       </c>
       <c r="R5" t="n">
-        <v>6709012</v>
+        <v>6709035</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119945297</v>
+        <v>119945284</v>
       </c>
       <c r="B6" t="n">
         <v>78542</v>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>435871</v>
+        <v>435879</v>
       </c>
       <c r="R6" t="n">
-        <v>6709030</v>
+        <v>6709025</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119945222</v>
+        <v>119945192</v>
       </c>
       <c r="B7" t="n">
-        <v>8432</v>
+        <v>78279</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>435948</v>
+        <v>435942</v>
       </c>
       <c r="R7" t="n">
-        <v>6708984</v>
+        <v>6708975</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119945518</v>
+        <v>119945909</v>
       </c>
       <c r="B8" t="n">
-        <v>86429</v>
+        <v>91902</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3690</v>
+        <v>5449</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>435894</v>
+        <v>435898</v>
       </c>
       <c r="R8" t="n">
-        <v>6709005</v>
+        <v>6709012</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119945424</v>
+        <v>119945297</v>
       </c>
       <c r="B9" t="n">
-        <v>91874</v>
+        <v>78542</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2059</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>435856</v>
+        <v>435871</v>
       </c>
       <c r="R9" t="n">
-        <v>6709035</v>
+        <v>6709030</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119945192</v>
+        <v>119945222</v>
       </c>
       <c r="B10" t="n">
-        <v>78279</v>
+        <v>8432</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,25 +1503,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>435942</v>
+        <v>435948</v>
       </c>
       <c r="R10" t="n">
-        <v>6708975</v>
+        <v>6708984</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 8305-2022 artfynd.xlsx
+++ b/artfynd/A 8305-2022 artfynd.xlsx
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119945284</v>
+        <v>119945192</v>
       </c>
       <c r="B6" t="n">
-        <v>78542</v>
+        <v>78279</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>435879</v>
+        <v>435942</v>
       </c>
       <c r="R6" t="n">
-        <v>6709025</v>
+        <v>6708975</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119945192</v>
+        <v>119945284</v>
       </c>
       <c r="B7" t="n">
-        <v>78279</v>
+        <v>78542</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>435942</v>
+        <v>435879</v>
       </c>
       <c r="R7" t="n">
-        <v>6708975</v>
+        <v>6709025</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 8305-2022 artfynd.xlsx
+++ b/artfynd/A 8305-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119945189</v>
+        <v>119945424</v>
       </c>
       <c r="B2" t="n">
-        <v>79160</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>2059</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>435946</v>
+        <v>435856</v>
       </c>
       <c r="R2" t="n">
-        <v>6708981</v>
+        <v>6709035</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119945182</v>
+        <v>119945518</v>
       </c>
       <c r="B3" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87325</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>3690</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>435945</v>
+        <v>435894</v>
       </c>
       <c r="R3" t="n">
-        <v>6708988</v>
+        <v>6709005</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,37 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119945518</v>
+        <v>119945174</v>
       </c>
       <c r="B4" t="n">
-        <v>86429</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3690</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>435894</v>
+        <v>435945</v>
       </c>
       <c r="R4" t="n">
-        <v>6709005</v>
+        <v>6708988</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,37 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119945424</v>
+        <v>119945284</v>
       </c>
       <c r="B5" t="n">
-        <v>91874</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2059</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>435856</v>
+        <v>435879</v>
       </c>
       <c r="R5" t="n">
-        <v>6709035</v>
+        <v>6709025</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,37 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119945192</v>
+        <v>119945297</v>
       </c>
       <c r="B6" t="n">
-        <v>78279</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>435942</v>
+        <v>435871</v>
       </c>
       <c r="R6" t="n">
-        <v>6708975</v>
+        <v>6709030</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,15 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119945284</v>
+        <v>119945189</v>
       </c>
       <c r="B7" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1201,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>435879</v>
+        <v>435946</v>
       </c>
       <c r="R7" t="n">
-        <v>6709025</v>
+        <v>6708981</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,37 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119945909</v>
+        <v>119945222</v>
       </c>
       <c r="B8" t="n">
-        <v>91902</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5449</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>435898</v>
+        <v>435948</v>
       </c>
       <c r="R8" t="n">
-        <v>6709012</v>
+        <v>6708984</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,15 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119945297</v>
+        <v>119945192</v>
       </c>
       <c r="B9" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1405,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>435871</v>
+        <v>435942</v>
       </c>
       <c r="R9" t="n">
-        <v>6709030</v>
+        <v>6708975</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1488,108 +1448,6 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>119945222</v>
-      </c>
-      <c r="B10" t="n">
-        <v>8432</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>106545</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Mindre märgborre</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Tomicus minor</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Våltjärnsflötten, Våltjärnsflötten, Dlr</t>
-        </is>
-      </c>
-      <c r="Q10" t="n">
-        <v>435948</v>
-      </c>
-      <c r="R10" t="n">
-        <v>6708984</v>
-      </c>
-      <c r="S10" t="n">
-        <v>10</v>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>Malung-Sälen</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>Malung</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>2024-09-24</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>2024-09-24</t>
-        </is>
-      </c>
-      <c r="AD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="inlineStr"/>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 8305-2022 artfynd.xlsx
+++ b/artfynd/A 8305-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119945424</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119945518</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119945174</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119945284</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119945297</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119945189</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119945222</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,8 +1488,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119945192</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>